--- a/credito.xlsx
+++ b/credito.xlsx
@@ -1,117 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisb\Desktop\Trabalho_P4\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66468D8A-0645-4576-BEDC-E30119E1892F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="3030" windowWidth="21600" windowHeight="11385" xr2:uid="{C5FFC5E2-503E-4BC0-A6EF-3B3CC968B4FB}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3030" yWindow="3030" windowWidth="21600" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>A — Cliente</t>
-  </si>
-  <si>
-    <t>B — Rendimento (€)</t>
-  </si>
-  <si>
-    <t>C — Dívida (€)</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
-    <t>Rendimento</t>
-  </si>
-  <si>
-    <t>Dívida</t>
-  </si>
-  <si>
-    <t>João Silva</t>
-  </si>
-  <si>
-    <t>Maria Costa</t>
-  </si>
-  <si>
-    <t>Pedro Ramos</t>
-  </si>
-  <si>
-    <t>Ana Ferreira</t>
-  </si>
-  <si>
-    <t>Rui Mendes</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -141,28 +66,84 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -482,92 +463,154 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB7FAA25-C5B2-49CE-97C3-5337E54A6585}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.7109375" customWidth="1"/>
-    <col min="2" max="2" width="37.140625" customWidth="1"/>
-    <col min="3" max="3" width="36.42578125" customWidth="1"/>
+    <col width="37.7109375" customWidth="1" min="1" max="1"/>
+    <col width="37.140625" customWidth="1" min="2" max="2"/>
+    <col width="36.42578125" customWidth="1" min="3" max="3"/>
+    <col width="20.140625" customWidth="1" min="4" max="4"/>
+    <col width="26.7109375" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
+    <row r="1" ht="45.75" customHeight="1" thickBot="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Rendimento</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Dívida</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rácio Dívida</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Decisão</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
+    <row r="2" ht="29.25" customHeight="1" thickBot="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>João Silva</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2">
-        <v>2000</v>
-      </c>
-      <c r="C3" s="2">
-        <v>400</v>
+    <row r="3" ht="29.25" customHeight="1" thickBot="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Maria Costa</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>800</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Recusado</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2">
+    <row r="4" ht="29.25" customHeight="1" thickBot="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Pedro Ramos</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="C4" s="2">
-        <v>700</v>
+      <c r="D4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2">
-        <v>3500</v>
-      </c>
-      <c r="C5" s="2">
-        <v>800</v>
+    <row r="5" ht="29.25" customHeight="1" thickBot="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Ana Ferreira</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1200</v>
-      </c>
-      <c r="C6" s="2">
-        <v>100</v>
+    <row r="6" ht="29.25" customHeight="1" thickBot="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Rui Mendes</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>950</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recusado</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2">
-        <v>950</v>
-      </c>
-      <c r="C7" s="2">
-        <v>600</v>
-      </c>
-    </row>
+    <row r="7" ht="29.25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/credito.xlsx
+++ b/credito.xlsx
@@ -1,39 +1,73 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisb\Desktop\Trabalho_P4\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921A0CEB-911D-45A2-98AB-AF9ECDDD8265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3030" yWindow="3030" windowWidth="21600" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="3030" yWindow="3030" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Rendimento</t>
+  </si>
+  <si>
+    <t>Dívida</t>
+  </si>
+  <si>
+    <t>João Silva</t>
+  </si>
+  <si>
+    <t>Maria Costa</t>
+  </si>
+  <si>
+    <t>Pedro Ramos</t>
+  </si>
+  <si>
+    <t>Ana Ferreira</t>
+  </si>
+  <si>
+    <t>Rui Mendes</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -67,83 +101,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -463,154 +438,84 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="37.7109375" customWidth="1" min="1" max="1"/>
-    <col width="37.140625" customWidth="1" min="2" max="2"/>
-    <col width="36.42578125" customWidth="1" min="3" max="3"/>
-    <col width="20.140625" customWidth="1" min="4" max="4"/>
-    <col width="26.7109375" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="37.7109375" customWidth="1"/>
+    <col min="2" max="2" width="37.140625" customWidth="1"/>
+    <col min="3" max="3" width="36.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45.75" customHeight="1" thickBot="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Rendimento</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Dívida</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Rácio Dívida</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Decisão</t>
-        </is>
+    <row r="1" spans="1:3" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="2" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>João Silva</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
+    <row r="2" spans="1:3" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
         <v>2000</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="1">
         <v>400</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
     </row>
-    <row r="3" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Maria Costa</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
+    <row r="3" spans="1:3" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
         <v>800</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="1">
         <v>700</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Recusado</t>
-        </is>
-      </c>
     </row>
-    <row r="4" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Pedro Ramos</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
+    <row r="4" spans="1:3" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
         <v>3500</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="1">
         <v>800</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
     </row>
-    <row r="5" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Ana Ferreira</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
+    <row r="5" spans="1:3" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
         <v>1200</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="1">
         <v>100</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
     </row>
-    <row r="6" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Rui Mendes</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
+    <row r="6" spans="1:3" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
         <v>950</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="1">
         <v>600</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Recusado</t>
-        </is>
-      </c>
     </row>
-    <row r="7" ht="29.25" customHeight="1"/>
+    <row r="7" spans="1:3" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
